--- a/「ClineでGitの小難しい部分をいかに簡単にできるか」調查.xlsx
+++ b/「ClineでGitの小難しい部分をいかに簡単にできるか」調查.xlsx
@@ -5,17 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\UPR2_work\TSET\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\UPR2_work\TSET\AI_TEST1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D092F9B-027C-4539-B0B9-E899B36C0407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A689505-F5A9-41E7-AB2F-143E78DC3321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="15" windowWidth="28770" windowHeight="15450" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="準備" sheetId="1" r:id="rId1"/>
     <sheet name="ブランチを作成" sheetId="3" r:id="rId2"/>
     <sheet name="マージ" sheetId="4" r:id="rId3"/>
+    <sheet name="pull最新然后提交当前分支" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
   <si>
     <t>①</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -139,6 +140,12 @@
   <si>
     <t>追加prompt：</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. メインブランチから現在のブランチに最新の変更をプルする。</t>
+  </si>
+  <si>
+    <t>2. 現在のブランチをコミットしてプッシュする。</t>
   </si>
 </sst>
 </file>
@@ -1092,6 +1099,55 @@
         <a:xfrm>
           <a:off x="874059" y="23801294"/>
           <a:ext cx="9428571" cy="6523809"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>26199</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>61403</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{656FE93E-8399-851B-904F-FC545AA4752E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="874059" y="1210235"/>
+          <a:ext cx="5561905" cy="6314286"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1533,4 +1589,40 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07E4A65E-3FE0-4316-A322-65E1BBD95BA9}">
+  <dimension ref="B3:D5"/>
+  <sheetFormatPr defaultColWidth="3.75" defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="1" width="3.75" style="1"/>
+    <col min="2" max="2" width="3.75" style="3"/>
+    <col min="3" max="16384" width="3.75" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:4">
+      <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4">
+      <c r="D4" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
+      <c r="D5" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/「ClineでGitの小難しい部分をいかに簡単にできるか」調查.xlsx
+++ b/「ClineでGitの小難しい部分をいかに簡単にできるか」調查.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\UPR2_work\TSET\AI_TEST1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\UPR2_work\TSET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A689505-F5A9-41E7-AB2F-143E78DC3321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A19D9D28-B0A4-4C86-B6B3-631DDFD61228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1148,6 +1148,94 @@
         <a:xfrm>
           <a:off x="874059" y="1210235"/>
           <a:ext cx="5561905" cy="6314286"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>43</xdr:col>
+      <xdr:colOff>178581</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>124375</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5389A53-F21C-D14F-6DE7-3556ECC15A35}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6992471" y="1210235"/>
+          <a:ext cx="5714286" cy="4561905"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>183221</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>109022</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DEC38737-15CD-9B82-B233-F7B20408A8A1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="874059" y="7866529"/>
+          <a:ext cx="8923809" cy="6361905"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
